--- a/data/test_cases.xlsx
+++ b/data/test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kimbal/Downloads/code/trackify-automation/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C3CEA0-BF66-174F-B698-DFADBE8F69C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D5A4BD-AE45-B045-9D91-EA16FD213A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -298,17 +298,17 @@
     <t>See docs/TECHNICAL_SPEC.md section 11 and docs/SCALING.md Q5-Q6.</t>
   </si>
   <si>
+    <t>transaction appears in Recent transactions with amount "5001.0"
+Transactions shows the saved transaction with matching date, amount, category, and time
+This Month summary is correct for budget "30000"</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>user taps "Add Income"
-user enters amount "5001"
+user enters amount "5002"
 user selects category "Salary"
 user enters tags "salary,work"
 user taps Save</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>transaction appears in Recent transactions with amount "5001.0"
-Transactions shows the saved transaction with matching date, amount, category, and time
-This Month summary is correct for budget "30000"</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -918,10 +918,10 @@
         <v>26</v>
       </c>
       <c r="N3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="P3" s="11">
         <v>34</v>
